--- a/Arquivos_GVR/dados_acareacoes_GVR.xlsx
+++ b/Arquivos_GVR/dados_acareacoes_GVR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320081488305</t>
+          <t>3320087485567</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Elaine Teixeira da Silva Costa</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5533991470638</t>
+          <t>+5533999502092</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rua Santos Fernandes 55 Ap, Periquito</t>
+          <t>Rua Waldomiro Barrel 87 Casa, Periquito</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BERMUDA FITNESS ACADEMIA CAMINHADA LAZER COM BOLSO LATERAL*1</t>
+          <t>Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1+Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1+Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-08 14:25:13</t>
+          <t>2026-06-09 13:27:41</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320081496191</t>
+          <t>3320075494860</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(GVL LOC) CLODOALDO DE PAULA</t>
+          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,44 +528,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>juceliajhu</t>
+          <t>Janaiara Alves de souza</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5533988181304</t>
+          <t>+5533991680170</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borba gato 484 484 interfone 2, Governador Valadares</t>
+          <t>Rua Bahia 466 Casa, Periquito</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Luva removedora de pelos pet tira pelo de cachorro e gato,limpe as roupas e a roupa de cama.*1</t>
+          <t>Lanterna T9 Tática Mais Forte Do Mundo Profissional Cor Da Luz Branca À prova d'água e resistente à chuva (IP-65), bateria recarregável*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-08 12:22:08</t>
+          <t>2026-06-09 13:25:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3320048492428</t>
+          <t>3320010500435</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+          <t>(GVL LOC) EDUARDO CALDEIRA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,79 +575,173 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Andréia Carla Ferraz Ferraz</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5533998738174</t>
+          <t>+5533998415847</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rua Bahia 366 366 Casa, Periquito</t>
+          <t>Rua Milão 137 apto 202, Governador Valadares</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kit Surpresa Romântica 500 Pétalas + 30 balões + 10 Velas + "TE AMO " Decoração Completa Dia dos Namorados*1</t>
+          <t>Escovas de Aço Multiuso Kit 3 Pcs Aço Latão Nylon Cabo Plástico*1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-08 12:09:14</t>
+          <t>2026-06-09 10:53:06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3320084484892</t>
+          <t>3320081488305</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Elaine Teixeira da Silva Costa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>+5533991470638</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rua Santos Fernandes 55 Ap, Periquito</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>BERMUDA FITNESS ACADEMIA CAMINHADA LAZER COM BOLSO LATERAL*1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-08 14:25:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3320081496191</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>(GVL LOC) CLODOALDO DE PAULA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Fake Delivery</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Andreia Pires</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>+5533984516758</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rua Monte Golgotá 165 Casa, Governador Valadares</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tônico de Crescimento Capilar Biovin-A Ultravin YouShine 200ml Spray*1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11.61</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-05 12:46:00</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>juceliajhu</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>+5533988181304</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Borba gato 484 484 interfone 2, Governador Valadares</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Luva removedora de pelos pet tira pelo de cachorro e gato,limpe as roupas e a roupa de cama.*1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:22:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3320048492428</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bernardo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+5533998738174</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rua Bahia 366 366 Casa, Periquito</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kit Surpresa Romântica 500 Pétalas + 30 balões + 10 Velas + "TE AMO " Decoração Completa Dia dos Namorados*1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>24.86</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-08 12:09:14</t>
         </is>
       </c>
     </row>

--- a/Arquivos_GVR/dados_acareacoes_GVR.xlsx
+++ b/Arquivos_GVR/dados_acareacoes_GVR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320087485567</t>
+          <t>3320053760423</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+          <t>(GVL INT) JACINTO DE SOUZA (ALVARENGA)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Vivian dos Santos Sabino torres</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5533999502092</t>
+          <t>+5533997049373</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rua Waldomiro Barrel 87 Casa, Periquito</t>
+          <t>rua Martins de Faria 09 perto do castelo, Alvarenga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1+Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1+Calça Jogger Moletom Ajuste na Cintura Cordão Elástico Reforçado Dia a Dia Inverno Calça Quentinha Mali Revenda*1</t>
+          <t>Ankle Boot Feminina Peep Toe Salto Bloco Médio 8cm Calce Fácil Elegante Confortável Santinho*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 13:27:41</t>
+          <t>2026-08-07 11:22:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320075494860</t>
+          <t>3320027716450</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+          <t>(GVL LOC) EDUARDO CALDEIRA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,44 +528,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Janaiara Alves de souza</t>
+          <t>GUSTAVO LIMA DE ANDRADE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5533991680170</t>
+          <t>+5533997031585</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rua Bahia 466 Casa, Periquito</t>
+          <t>Rua Trinta de Janeiro 100 CASA, Governador Valadares</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanterna T9 Tática Mais Forte Do Mundo Profissional Cor Da Luz Branca À prova d'água e resistente à chuva (IP-65), bateria recarregável*1</t>
+          <t>KIT 10 PEÇAS ARRUELA PARAFUSO M6 JDM 8 CORES ALUMÍNIO, PARA CARRO E MOTO*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-09 13:25:25</t>
+          <t>2026-08-07 11:21:56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3320010500435</t>
+          <t>3320082745386</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(GVL LOC) EDUARDO CALDEIRA</t>
+          <t>(GVR INT) SAULO DE TARSO (TARUMIRIM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,44 +575,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Andréia Carla Ferraz Ferraz</t>
+          <t>Erika silveira</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5533998415847</t>
+          <t>+5533999657325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rua Milão 137 apto 202, Governador Valadares</t>
+          <t>Av nossa senhora conceição 271 escola, Tarumirim</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Escovas de Aço Multiuso Kit 3 Pcs Aço Latão Nylon Cabo Plástico*1</t>
+          <t>KIT com 2 Calcinha modeladora cintura alta com Barbatanas para afinar cintura 20cm CORES E/OU*2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>8.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-09 10:53:06</t>
+          <t>2026-08-07 11:20:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3320081488305</t>
+          <t>3320097754861</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+          <t>(GVL INT) BARCENICIO GERALDO (ITANHOMI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,44 +622,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Elaine Teixeira da Silva Costa</t>
+          <t>Tiago Siqueira</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+5533991470638</t>
+          <t>+5533998161465</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rua Santos Fernandes 55 Ap, Periquito</t>
+          <t>rua Antônio Frederico neuba 135 padaria doce sabor, Itanhomi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BERMUDA FITNESS ACADEMIA CAMINHADA LAZER COM BOLSO LATERAL*1</t>
+          <t>Caixa de Som Bluetooth G200 Magnética Amplificador Portátil para Celular*1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-08 14:25:13</t>
+          <t>2026-08-07 11:20:41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3320081496191</t>
+          <t>3320075740785</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(GVL LOC) CLODOALDO DE PAULA</t>
+          <t>(GVR LOC) LUCAS DE OLIVEIRA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -669,44 +669,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>juceliajhu</t>
+          <t>giovanna alves</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+5533988181304</t>
+          <t>+5533991251439</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borba gato 484 484 interfone 2, Governador Valadares</t>
+          <t>Rua Joaquim Ribeiro Nascimento 178 casa, Governador Valadares</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Luva removedora de pelos pet tira pelo de cachorro e gato,limpe as roupas e a roupa de cama.*1</t>
+          <t>Anéis Ajustáveis Femininos Dourados em Aço Inoxidável Premium | Minimalistas, Hipoalergênicos e Resistentes à Água*1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-08 12:22:08</t>
+          <t>2026-08-07 09:48:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3320048492428</t>
+          <t>6072526390238</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(GVL INT) MIRELA IVANETE (NAQUE)</t>
+          <t>(GVL INT) JACINTO DE SOUZA (ALVARENGA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,32 +716,220 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Rosana Prado522</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+5533998738174</t>
+          <t>+5533998153357</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rua Bahia 366 366 Casa, Periquito</t>
+          <t>Rua das palmeiras(serraria),05,Casa 05, Periquito</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kit Surpresa Romântica 500 Pétalas + 30 balões + 10 Velas + "TE AMO " Decoração Completa Dia dos Namorados*1</t>
+          <t>Shampoo de tintura de cabelo 3 em 1-500ML COR PRETO ENVIO IMEDIATO/500ML ESC 1*1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-08 12:09:14</t>
+          <t>2026-08-06 15:31:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3320092756925</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(GVL INT) JONATAS JOSUE (DIVINOLANDIA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Raquel Souza</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>+5533988462978</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rua monsenhor Ayala 19 loja agropecuária kibarato, Divinolândia de Minas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blusa com babados + short saia - look fashion para meninas*1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>44.11</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3320030748039</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(GVL INT) BARCENICIO GERALDO (ITANHOMI)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cristina Maria Rosa Chaga</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+5533999255915</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rua Governador Valadares 403 Casa, Capitão Andrade</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dedeira de Silicone Anti-Odor – Protetor para Calos &amp; Unha Encravada | Dedos dos Pés &amp; Mãos*2+Kit 36/100 Adesivo Seca Espinha, Anti‐acne, Transparente Invisível Dia/Noite Secativo*1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3320068761805</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(GVL INT) JONATAS JOSUE (DIVINOLANDIA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flávia aparecida de oliveira</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>+5533984612975</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>rua padre Tiago 1 sim, Divinolândia de Minas</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calça Pantalona Estampado Elastico Na cintura Bolsos*1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3320000773345</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(GVL INT) JONATAS JOSUE (DIVINOLANDIA)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fake Delivery</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Flávia aparecida de oliveira</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>+5533984612975</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>rua padre Tiago 1 sim, Divinolândia de Minas</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calça Feminina Pantalona Wide Leg Duna Com Elastico Na Cintura Corda Decorativa P-M-G-GG*1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>21.99</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:07</t>
         </is>
       </c>
     </row>
